--- a/연구코드/aec/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/aec/results/regression/gangnam/all/regression_results.xlsx
@@ -792,10 +792,10 @@
         <v>0.6675672465916966</v>
       </c>
       <c r="D2">
-        <v>0.6668746762221173</v>
+        <v>0.6668746762221172</v>
       </c>
       <c r="E2">
-        <v>0.6643031832395616</v>
+        <v>0.6643031832395617</v>
       </c>
       <c r="F2">
         <v>0.6721946227110475</v>
@@ -806,19 +806,19 @@
         <v>28</v>
       </c>
       <c r="B3">
-        <v>0.6451095718129778</v>
+        <v>0.6451095718129779</v>
       </c>
       <c r="C3">
         <v>0.6478795581647603</v>
       </c>
       <c r="D3">
-        <v>0.6386437247173653</v>
+        <v>0.6386437247173652</v>
       </c>
       <c r="E3">
         <v>0.6586217093918358</v>
       </c>
       <c r="F3">
-        <v>0.6461530403070868</v>
+        <v>0.6461530403070865</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -826,7 +826,7 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>0.667288996981806</v>
+        <v>0.6672889969818059</v>
       </c>
       <c r="C4">
         <v>0.679189945684151</v>
@@ -835,10 +835,10 @@
         <v>0.6784998926389717</v>
       </c>
       <c r="E4">
-        <v>0.6719841302816145</v>
+        <v>0.6719841302816141</v>
       </c>
       <c r="F4">
-        <v>0.673705159514414</v>
+        <v>0.6737051595144141</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -849,13 +849,13 @@
         <v>0.551732293323334</v>
       </c>
       <c r="C5">
-        <v>0.5330123872154995</v>
+        <v>0.5330123872154993</v>
       </c>
       <c r="D5">
         <v>0.5471761009181475</v>
       </c>
       <c r="E5">
-        <v>0.5039493231467151</v>
+        <v>0.5039493231467155</v>
       </c>
       <c r="F5">
         <v>0.5280622039976861</v>
@@ -869,13 +869,13 @@
         <v>0.6610064116087828</v>
       </c>
       <c r="C6">
-        <v>0.6721407222061696</v>
+        <v>0.6721407222061697</v>
       </c>
       <c r="D6">
-        <v>0.6730185702913063</v>
+        <v>0.6730185702913065</v>
       </c>
       <c r="E6">
-        <v>0.6742709587393536</v>
+        <v>0.6742709587393538</v>
       </c>
       <c r="F6">
         <v>0.6760315888360582</v>
